--- a/Pasos.xlsx
+++ b/Pasos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Esau\Documents\Rutas\R2104-001 Refurbish\Archivos para VS Code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3E53CC3-8F87-4318-9DA5-971FC8C86E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ACA5D38-5082-439D-A2CD-8C450FB0E373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{5795E6C4-582A-4966-B1F2-A8415208E702}"/>
   </bookViews>
@@ -25,90 +25,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="28">
-  <si>
-    <t xml:space="preserve"> ############################################################################################</t>
-  </si>
-  <si>
-    <t>MODO EDIT - SECUENCIA DE GUARDADO DE PROGRAMA</t>
-  </si>
-  <si>
-    <t>############################################################################################</t>
-  </si>
-  <si>
-    <t>================================================================================</t>
-  </si>
-  <si>
-    <t>Trigger</t>
-  </si>
-  <si>
-    <t>#PASO 10</t>
-  </si>
-  <si>
-    <t>1. Se desenclava bit de estado.</t>
-  </si>
-  <si>
-    <t>2. Se mueve a cero puntero índice.</t>
-  </si>
-  <si>
-    <t>#PASO 20</t>
-  </si>
-  <si>
-    <t>1. Se mueven las posiciones de robot según el índice en programa seleccionado.</t>
-  </si>
-  <si>
-    <t>2. Se actualiza bit de dispensado según el índice en programa seleccionado.</t>
-  </si>
-  <si>
-    <t>#PASO 30</t>
-  </si>
-  <si>
-    <t>1. Se incrementa en 1 valor de indice.</t>
-  </si>
-  <si>
-    <t>#PASO 40</t>
-  </si>
-  <si>
-    <t>1. Si valor de índice es menor que número de elementos de programa, secuencia se mueve al paso 20.</t>
-  </si>
-  <si>
-    <t>2. Si valor de índice es mayor o igual a número de elementos de programa, secuencia continua.</t>
-  </si>
-  <si>
-    <t>#PASO 50</t>
-  </si>
-  <si>
-    <t>1. Se enclava bit de secuencia finalizada correctamente.</t>
-  </si>
-  <si>
-    <t>#PASO 0</t>
-  </si>
-  <si>
-    <t>1. Finaliza secuencia.</t>
-  </si>
-  <si>
-    <t>Tiempo</t>
-  </si>
-  <si>
-    <t>100ms</t>
-  </si>
-  <si>
-    <t>OTL</t>
-  </si>
-  <si>
-    <t>Salida para activar siguiente paso</t>
-  </si>
-  <si>
-    <t>TON</t>
-  </si>
-  <si>
-    <t>DRIVER DEL PASO</t>
-  </si>
-  <si>
-    <t>Movimiento de datos</t>
-  </si>
-  <si>
-    <t>MOVE</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+  <si>
+    <t>ID_Paso</t>
+  </si>
+  <si>
+    <t>Tag_Paso</t>
+  </si>
+  <si>
+    <t>Condicion_Transicion</t>
+  </si>
+  <si>
+    <t>Tiempo_Limite_MS</t>
+  </si>
+  <si>
+    <t>Paso_Inicial</t>
+  </si>
+  <si>
+    <t>Paso_Llenado</t>
+  </si>
+  <si>
+    <t>Paso_Mezcla</t>
+  </si>
+  <si>
+    <t>Boton_Start</t>
+  </si>
+  <si>
+    <t>Sensor_Nivel_Max</t>
+  </si>
+  <si>
+    <t>Paso_MueveAlPaso0</t>
+  </si>
+  <si>
+    <t>No hay</t>
+  </si>
+  <si>
+    <t>Paso_Enclava_Bit</t>
+  </si>
+  <si>
+    <t>T_Paso_30.DN</t>
+  </si>
+  <si>
+    <t>T_Paso_40.DN</t>
   </si>
 </sst>
 </file>
@@ -124,18 +82,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -152,7 +104,9 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -467,203 +421,98 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D898608-59FD-481B-9717-8549C17666AB}">
-  <dimension ref="A1:E33"/>
+  <dimension ref="B2:F7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="92.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="63.42578125" customWidth="1"/>
+    <col min="1" max="1" width="4.85546875" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" style="1"/>
+    <col min="3" max="4" width="44" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.85546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="44" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B3" s="1">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="1">
+        <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B4" s="1">
+        <v>20</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="1">
+        <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" t="s">
-        <v>5</v>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="1">
+        <v>30</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="1">
+        <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
-        <v>25</v>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B6" s="1">
+        <v>40</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="1">
+        <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B7" s="1">
+        <v>0</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="D7" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>3</v>
+      <c r="E7" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
